--- a/filebaocaov2.xlsx
+++ b/filebaocaov2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="70">
   <si>
     <t>Mã tỉnh chấp nhận</t>
   </si>
@@ -230,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +257,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -285,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -427,11 +435,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -486,6 +503,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -787,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -799,7 +823,7 @@
     <col min="12" max="12" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="27.6" customHeight="1" thickBot="1">
+    <row r="1" spans="1:37" ht="27.6" customHeight="1" thickBot="1">
       <c r="A1" s="3"/>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -851,8 +875,12 @@
       <c r="AG1" s="14"/>
       <c r="AH1" s="14"/>
       <c r="AI1" s="15"/>
-    </row>
-    <row r="2" spans="1:35" ht="144.6" thickBot="1">
+      <c r="AJ1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK1" s="21"/>
+    </row>
+    <row r="2" spans="1:37" ht="144.6" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>42</v>
       </c>
@@ -958,8 +986,14 @@
       <c r="AI2" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:35">
+      <c r="AJ2" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK2" s="22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1012,7 +1046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:35">
+    <row r="4" spans="1:37">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1065,7 +1099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:37">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1118,7 +1152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:37">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1171,7 +1205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:37">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1224,7 +1258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:35">
+    <row r="8" spans="1:37">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1277,7 +1311,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:37">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1330,7 +1364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:37">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1383,7 +1417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:37">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1436,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:37">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1489,7 +1523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:37">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1542,7 +1576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:37">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1595,7 +1629,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:37">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1648,7 +1682,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:37">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2921,7 +2955,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="R1:U1"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="AA1:AE1"/>
